--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -1279,7 +1279,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119888848</v>
+        <v>119885854</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538754</v>
+        <v>538796</v>
       </c>
       <c r="R7" t="n">
-        <v>6718142</v>
+        <v>6718150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1400,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119886330</v>
+        <v>119888848</v>
       </c>
       <c r="B8" t="n">
         <v>91840</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538706</v>
+        <v>538754</v>
       </c>
       <c r="R8" t="n">
-        <v>6718241</v>
+        <v>6718142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119885854</v>
+        <v>119886330</v>
       </c>
       <c r="B9" t="n">
         <v>91840</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538796</v>
+        <v>538706</v>
       </c>
       <c r="R9" t="n">
-        <v>6718150</v>
+        <v>6718241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -1279,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119885854</v>
+        <v>119888848</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538796</v>
+        <v>538754</v>
       </c>
       <c r="R7" t="n">
-        <v>6718150</v>
+        <v>6718142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119888848</v>
+        <v>119885854</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538754</v>
+        <v>538796</v>
       </c>
       <c r="R8" t="n">
-        <v>6718142</v>
+        <v>6718150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,7 +1524,7 @@
         <v>119886330</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -1279,7 +1279,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119888848</v>
+        <v>119885854</v>
       </c>
       <c r="B7" t="n">
         <v>91858</v>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538754</v>
+        <v>538796</v>
       </c>
       <c r="R7" t="n">
-        <v>6718142</v>
+        <v>6718150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1400,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119885854</v>
+        <v>119888848</v>
       </c>
       <c r="B8" t="n">
         <v>91858</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538796</v>
+        <v>538754</v>
       </c>
       <c r="R8" t="n">
-        <v>6718150</v>
+        <v>6718142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -1279,7 +1279,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119885854</v>
+        <v>119886330</v>
       </c>
       <c r="B7" t="n">
         <v>91858</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538796</v>
+        <v>538706</v>
       </c>
       <c r="R7" t="n">
-        <v>6718150</v>
+        <v>6718241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1400,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119888848</v>
+        <v>119885854</v>
       </c>
       <c r="B8" t="n">
         <v>91858</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538754</v>
+        <v>538796</v>
       </c>
       <c r="R8" t="n">
-        <v>6718142</v>
+        <v>6718150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119886330</v>
+        <v>119888848</v>
       </c>
       <c r="B9" t="n">
         <v>91858</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538706</v>
+        <v>538754</v>
       </c>
       <c r="R9" t="n">
-        <v>6718241</v>
+        <v>6718142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -1279,7 +1279,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119886330</v>
+        <v>119888848</v>
       </c>
       <c r="B7" t="n">
         <v>91858</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538706</v>
+        <v>538754</v>
       </c>
       <c r="R7" t="n">
-        <v>6718241</v>
+        <v>6718142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1400,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119885854</v>
+        <v>119886330</v>
       </c>
       <c r="B8" t="n">
         <v>91858</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538796</v>
+        <v>538706</v>
       </c>
       <c r="R8" t="n">
-        <v>6718150</v>
+        <v>6718241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119888848</v>
+        <v>119885854</v>
       </c>
       <c r="B9" t="n">
         <v>91858</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538754</v>
+        <v>538796</v>
       </c>
       <c r="R9" t="n">
-        <v>6718142</v>
+        <v>6718150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51999-2020 artfynd.xlsx
+++ b/artfynd/A 51999-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1640,6 +1640,354 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128875101</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rottnebyskogen , Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>538657</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6718303</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128874981</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rottnebyskogen , Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>538727</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6718222</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128874950</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rottnebyskogen , Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>538726</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6718204</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
